--- a/Clean_data/clean_gold_master.xlsx
+++ b/Clean_data/clean_gold_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOWNLOADS new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Research_Project_colab_TSA_DATA\Clean_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC271763-01D7-49B6-8B6D-E5054D3962AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C940BD-173B-4B1C-9B30-4E5ABD9527E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -997,12 +997,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1032,12 +1038,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1345,4438 +1354,4439 @@
   <dimension ref="A1:D316"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>2945</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>4510.75</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>3104</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>4712.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2974</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>4541.8999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>2895</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>4462.0600000000004</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>2851</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>4371.1400000000003</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>2948</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>4522.95</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>2924</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>4530.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>2830</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>4517.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>2834</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>4517.78</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>2800</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>4536.32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>2752</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>4484.55</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>2811</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>4544</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>2751</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>11.50233897</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>4468.41</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>2711</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>11.502274659999999</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>4373.33</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>2725</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>11.502274659999999</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>4269.74</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>2695</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>11.502274659999999</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>4264.17</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>2816</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>11.502146059999999</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>4435</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>2798</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>11.502081759999999</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>4400.4799999999996</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>2771</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>4380.71</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>2817</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>4446.67</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>2925</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>4618</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>2937</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>4700.26</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>2862</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>11.50224251</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>4601.5600000000004</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>2856</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>11.50224251</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>4578.42</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>2913</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>4690.43</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>3052</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>4905.25</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>3047</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>4914.0600000000004</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>3131</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>5047.37</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>3249</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>5229.5200000000004</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>3330</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>5308.16</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>3248</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>5187.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="3">
         <v>3208</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <v>5127.25</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>3300</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>5235.29</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="3">
         <v>3278</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
         <v>5223.8100000000004</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="3">
         <v>3303</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>5241.18</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="3">
         <v>3444</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>5437.38</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="3">
         <v>3688</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>5750.87</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="3">
         <v>3725</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>5814.23</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="3">
         <v>3534</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <v>5454.71</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="3">
         <v>3389</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>5190.3100000000004</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="3">
         <v>3673</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>5562.86</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="3">
         <v>3698</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>5514.52</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="3">
         <v>3628</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>5358.57</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="3">
         <v>3720</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>5452.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="3">
         <v>3919</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>5697.35</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="3">
         <v>3920</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>5697.25</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="3">
         <v>4038</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>5838.61</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="3">
         <v>4215</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>6093.64</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="3">
         <v>4289</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>6186.43</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="3">
         <v>4190</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3">
         <v>11.502210359999999</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>6037.11</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="3">
         <v>4198</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="3">
         <v>11.50211391</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>5985.23</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="3">
         <v>4191</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="3">
         <v>11.50211391</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="3">
         <v>5904.75</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="3">
         <v>3974</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3">
         <v>11.50204961</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>5742.86</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="3">
         <v>4057</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3">
         <v>11.50204961</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <v>5860.48</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="3">
         <v>4123</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="3">
         <v>11.50204961</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <v>6057.62</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="3">
         <v>4140</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="3">
         <v>11.50198531</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>6120.48</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="3">
         <v>4192</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="3">
         <v>11.50198531</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <v>6168.95</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="3">
         <v>4351</v>
       </c>
-      <c r="C59" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="C59" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D59" s="3">
         <v>6360.56</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="3">
         <v>4540</v>
       </c>
-      <c r="C60" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="C60" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D60" s="3">
         <v>6542.94</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="3">
         <v>4582</v>
       </c>
-      <c r="C61" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C61" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D61" s="3">
         <v>6439.57</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="3">
         <v>4390</v>
       </c>
-      <c r="C62" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="C62" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D62" s="3">
         <v>6148.42</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="3">
         <v>4376</v>
       </c>
-      <c r="C63" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="C63" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D63" s="3">
         <v>6097.65</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="3">
         <v>4500</v>
       </c>
-      <c r="C64" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="C64" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D64" s="3">
         <v>6273.06</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="3">
         <v>4443</v>
       </c>
-      <c r="C65" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="C65" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D65" s="3">
         <v>6158</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="3">
         <v>4376</v>
       </c>
-      <c r="C66" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="C66" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D66" s="3">
         <v>6034.55</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="3">
         <v>4453</v>
       </c>
-      <c r="C67" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="C67" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D67" s="3">
         <v>6132.27</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="3">
         <v>4395</v>
       </c>
-      <c r="C68" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="C68" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D68" s="3">
         <v>6059.21</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="3">
         <v>4535</v>
       </c>
-      <c r="C69" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C69" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D69" s="3">
         <v>6244.76</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="3">
         <v>4712</v>
       </c>
-      <c r="C70" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="C70" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D70" s="3">
         <v>6540.48</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="3">
         <v>4864</v>
       </c>
-      <c r="C71" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C71" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D71" s="3">
         <v>6876.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="3">
         <v>4925</v>
       </c>
-      <c r="C72" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C72" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D72" s="3">
         <v>7153.16</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="3">
         <v>5274</v>
       </c>
-      <c r="C73" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="C73" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D73" s="3">
         <v>7582.27</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="3">
         <v>5680</v>
       </c>
-      <c r="C74" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="C74" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D74" s="3">
         <v>7917</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="3">
         <v>5747</v>
       </c>
-      <c r="C75" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="C75" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D75" s="3">
         <v>8024.21</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="3">
         <v>5755</v>
       </c>
-      <c r="C76" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D76" s="2">
+      <c r="C76" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D76" s="3">
         <v>8070</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="3">
         <v>6301</v>
       </c>
-      <c r="C77" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D77" s="2">
+      <c r="C77" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D77" s="3">
         <v>8987.06</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="3">
         <v>7010</v>
       </c>
-      <c r="C78" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D78" s="2">
+      <c r="C78" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D78" s="3">
         <v>9965</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="3">
         <v>6180</v>
       </c>
-      <c r="C79" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D79" s="2">
+      <c r="C79" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D79" s="3">
         <v>8941.14</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="3">
         <v>6557</v>
       </c>
-      <c r="C80" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D80" s="2">
+      <c r="C80" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D80" s="3">
         <v>9574.4699999999993</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="3">
         <v>6538</v>
       </c>
-      <c r="C81" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D81" s="2">
+      <c r="C81" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D81" s="3">
         <v>9556.9</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="3">
         <v>6202</v>
       </c>
-      <c r="C82" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D82" s="2">
+      <c r="C82" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D82" s="3">
         <v>9002.25</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="3">
         <v>6068</v>
       </c>
-      <c r="C83" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D83" s="2">
+      <c r="C83" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D83" s="3">
         <v>8700.2099999999991</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="3">
         <v>6494</v>
       </c>
-      <c r="C84" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D84" s="2">
+      <c r="C84" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D84" s="3">
         <v>9137.73</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="3">
         <v>6517</v>
       </c>
-      <c r="C85" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D85" s="2">
+      <c r="C85" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D85" s="3">
         <v>9135.5300000000007</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="3">
         <v>6529</v>
       </c>
-      <c r="C86" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D86" s="2">
+      <c r="C86" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D86" s="3">
         <v>9065.2800000000007</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="3">
         <v>6883</v>
       </c>
-      <c r="C87" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D87" s="2">
+      <c r="C87" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D87" s="3">
         <v>9543.24</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="3">
         <v>6784</v>
       </c>
-      <c r="C88" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="C88" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D88" s="3">
         <v>9377.5</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="3">
         <v>7036</v>
       </c>
-      <c r="C89" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D89" s="2">
+      <c r="C89" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D89" s="3">
         <v>9322</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="3">
         <v>6911</v>
       </c>
-      <c r="C90" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D90" s="2">
+      <c r="C90" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D90" s="3">
         <v>8871.75</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="3">
         <v>6787</v>
       </c>
-      <c r="C91" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D91" s="2">
+      <c r="C91" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D91" s="3">
         <v>8698.33</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="3">
         <v>6887</v>
       </c>
-      <c r="C92" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D92" s="2">
+      <c r="C92" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D92" s="3">
         <v>8744.5499999999993</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="3">
         <v>6881</v>
       </c>
-      <c r="C93" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D93" s="2">
+      <c r="C93" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D93" s="3">
         <v>8821.19</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="3">
         <v>7367</v>
       </c>
-      <c r="C94" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D94" s="2">
+      <c r="C94" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D94" s="3">
         <v>9322.7800000000007</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="3">
         <v>7811</v>
       </c>
-      <c r="C95" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D95" s="2">
+      <c r="C95" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D95" s="3">
         <v>9685.4500000000007</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="3">
         <v>8357</v>
       </c>
-      <c r="C96" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D96" s="2">
+      <c r="C96" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D96" s="3">
         <v>10311.67</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="3">
         <v>8328</v>
       </c>
-      <c r="C97" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D97" s="2">
+      <c r="C97" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D97" s="3">
         <v>10290.790000000001</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="3">
         <v>9199</v>
       </c>
-      <c r="C98" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D98" s="2">
+      <c r="C98" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D98" s="3">
         <v>11295</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="3">
         <v>9558</v>
       </c>
-      <c r="C99" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="C99" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D99" s="3">
         <v>11892.4</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="3">
         <v>10039</v>
       </c>
-      <c r="C100" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D100" s="2">
+      <c r="C100" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D100" s="3">
         <v>12638.95</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="3">
         <v>9427</v>
       </c>
-      <c r="C101" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D101" s="2">
+      <c r="C101" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D101" s="3">
         <v>11814.75</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="3">
         <v>9202</v>
       </c>
-      <c r="C102" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D102" s="2">
+      <c r="C102" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D102" s="3">
         <v>12220</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="3">
         <v>9208</v>
       </c>
-      <c r="C103" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D103" s="2">
+      <c r="C103" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D103" s="3">
         <v>12352.14</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="3">
         <v>9735</v>
       </c>
-      <c r="C104" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D104" s="2">
+      <c r="C104" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D104" s="3">
         <v>13023.91</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="3">
         <v>8692</v>
       </c>
-      <c r="C105" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D105" s="2">
+      <c r="C105" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D105" s="3">
         <v>11835.75</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="3">
         <v>8565</v>
       </c>
-      <c r="C106" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D106" s="2">
+      <c r="C106" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D106" s="3">
         <v>12218.57</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="3">
         <v>8382</v>
       </c>
-      <c r="C107" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D107" s="2">
+      <c r="C107" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D107" s="3">
         <v>12755</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="3">
         <v>7861</v>
       </c>
-      <c r="C108" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D108" s="2">
+      <c r="C108" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D108" s="3">
         <v>12162.75</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="3">
         <v>8485</v>
       </c>
-      <c r="C109" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D109" s="2">
+      <c r="C109" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D109" s="3">
         <v>12923.86</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="3">
         <v>8884</v>
       </c>
-      <c r="C110" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D110" s="2">
+      <c r="C110" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D110" s="3">
         <v>13481.05</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="3">
         <v>9746</v>
       </c>
-      <c r="C111" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D111" s="2">
+      <c r="C111" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D111" s="3">
         <v>14778.68</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="3">
         <v>9577</v>
       </c>
-      <c r="C112" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D112" s="2">
+      <c r="C112" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D112" s="3">
         <v>15215</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="3">
         <v>9231</v>
       </c>
-      <c r="C113" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D113" s="2">
+      <c r="C113" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D113" s="3">
         <v>14485.06</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="3">
         <v>9604</v>
       </c>
-      <c r="C114" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D114" s="2">
+      <c r="C114" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D114" s="3">
         <v>14602</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="3">
         <v>9800</v>
       </c>
-      <c r="C115" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D115" s="2">
+      <c r="C115" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D115" s="3">
         <v>14648.18</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="3">
         <v>9671</v>
       </c>
-      <c r="C116" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D116" s="2">
+      <c r="C116" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D116" s="3">
         <v>14737.05</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="3">
         <v>9828</v>
       </c>
-      <c r="C117" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D117" s="2">
+      <c r="C117" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D117" s="3">
         <v>14960</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="3">
         <v>10316</v>
       </c>
-      <c r="C118" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D118" s="2">
+      <c r="C118" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D118" s="3">
         <v>15678.16</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="3">
         <v>10800</v>
       </c>
-      <c r="C119" s="2">
-        <v>11.501953159999999</v>
-      </c>
-      <c r="D119" s="2">
+      <c r="C119" s="3">
+        <v>11.501953159999999</v>
+      </c>
+      <c r="D119" s="3">
         <v>15870.28</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="3">
         <v>18182</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="3">
         <v>17050.95</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="3">
         <v>18292</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="3">
         <v>17129.57</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="3">
         <v>18056</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="3">
         <v>16725.259999999998</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="3">
         <v>17920</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="3">
         <v>16515.830000000002</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="3">
         <v>17986</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="3">
         <v>16624</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="3">
         <v>18537</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="3">
         <v>16681.189999999999</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="3">
         <v>19423</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="3">
         <v>18058.25</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="3">
         <v>19894</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="3">
         <v>18729.32</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="3">
         <v>19278</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="3">
         <v>18267.86</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="3">
         <v>20008</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="3">
         <v>18475.48</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="3">
         <v>20516</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="3">
         <v>19090.830000000002</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="3">
         <v>21668</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="3">
         <v>19496.669999999998</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="3">
         <v>22124</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="3">
         <v>20136</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="3">
         <v>22470</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="3">
         <v>20511.09</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="3">
         <v>21924</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="3">
         <v>20212.25</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="3">
         <v>22143</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="3">
         <v>20325.5</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="3">
         <v>22972</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="3">
         <v>20839.77</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="3">
         <v>23790</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="3">
         <v>21476.94</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="3">
         <v>24391</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="3">
         <v>22137.62</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="3">
         <v>24668</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="3">
         <v>22304.32</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="3">
         <v>25349</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="3">
         <v>22646.75</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="3">
         <v>28319</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="3">
         <v>25826.25</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="3">
         <v>28667</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="3">
         <v>27462.86</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="3">
         <v>26896</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="3">
         <v>26570.880000000001</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="3">
         <v>28041</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="3">
         <v>28542.75</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="3">
         <v>26620</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="3">
         <v>28093.57</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="3">
         <v>26728</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="3">
         <v>27574.75</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="3">
         <v>28128</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="3">
         <v>28137.37</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="3">
         <v>27023</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="3">
         <v>27731</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="3">
         <v>26618</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="3">
         <v>28601.79</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="3">
         <v>25585</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="3">
         <v>28812.25</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="3">
         <v>25760</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="3">
         <v>29807.25</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
+      <c r="A152" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="3">
         <v>25715</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="3">
         <v>29511.82</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
+      <c r="A153" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="3">
         <v>26239</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="3">
         <v>30222.78</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="3">
         <v>28133</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="3">
         <v>31651.39</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+      <c r="A155" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="3">
         <v>28189</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="3">
         <v>31045</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="3">
         <v>27803</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="3">
         <v>31535.56</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="3">
         <v>27220</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C157" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="3">
         <v>30827.5</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158" s="3">
         <v>26975</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C158" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="3">
         <v>30527.05</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="3">
         <v>26292</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C159" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="3">
         <v>29936.39</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
+      <c r="A160" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="3">
         <v>25692</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="3">
         <v>29511.58</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
+      <c r="A161" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="3">
         <v>23974.1</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C161" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="3">
         <v>27718.42</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162" s="3">
         <v>22836</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C162" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="3">
         <v>26852.27</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
+      <c r="A163" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="3">
         <v>21555.5</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="3">
         <v>27196.25</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
+      <c r="A164" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164" s="3">
         <v>20747</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="3">
         <v>26970.65</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
+      <c r="A165" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="3">
         <v>21724.1</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D165" s="2">
+      <c r="D165" s="3">
         <v>30178.82</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
+      <c r="A166" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166" s="3">
         <v>21765.4</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="3">
         <v>30489.21</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
+      <c r="A167" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="3">
         <v>21227.3</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="3">
         <v>30712.38</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
+      <c r="A168" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168" s="3">
         <v>20603.099999999999</v>
       </c>
-      <c r="C168" s="2">
+      <c r="C168" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="3">
         <v>30800.560000000001</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
+      <c r="A169" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169" s="3">
         <v>19724.5</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="3">
         <v>30033</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
+      <c r="A170" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="3">
         <v>20075.7</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C170" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="3">
         <v>29786.959999999999</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
+      <c r="A171" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171" s="3">
         <v>20978</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="3">
         <v>30450.28</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
+      <c r="A172" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172" s="3">
         <v>21566.799999999999</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D172" s="2">
+      <c r="D172" s="3">
         <v>30000</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="2" t="s">
+      <c r="A173" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173" s="3">
         <v>20965.8</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="3">
         <v>29569.439999999999</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
+      <c r="A174" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174" s="3">
         <v>20790.3</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="3">
         <v>29053.33</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
+      <c r="A175" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175" s="3">
         <v>20634.900000000001</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="3">
         <v>27625.24</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
+      <c r="A176" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176" s="3">
         <v>21173.8</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176" s="3">
         <v>17.932097670000001</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="3">
         <v>28219.57</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
+      <c r="A177" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="3">
         <v>20933.2</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="3">
         <v>28393.42</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
+      <c r="A178" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178" s="3">
         <v>20013.400000000001</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C178" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="3">
         <v>27332.73</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
+      <c r="A179" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179" s="3">
         <v>19738.400000000001</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="3">
         <v>27321.67</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
+      <c r="A180" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180" s="3">
         <v>18985.2</v>
       </c>
-      <c r="C180" s="2">
+      <c r="C180" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="3">
         <v>26417.5</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
+      <c r="A181" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181" s="3">
         <v>19377.8</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="3">
         <v>26943.18</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
+      <c r="A182" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182" s="3">
         <v>20183.2</v>
       </c>
-      <c r="C182" s="2">
+      <c r="C182" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="3">
         <v>27642.86</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
+      <c r="A183" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183" s="3">
         <v>19837</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="3">
         <v>27478.95</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
+      <c r="A184" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184" s="3">
         <v>19038</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184" s="3">
         <v>17.932139469999999</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="3">
         <v>26511.9</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="2" t="s">
+      <c r="A185" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185" s="3">
         <v>19335.7</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D185" s="2">
+      <c r="D185" s="3">
         <v>27010</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
+      <c r="A186" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186" s="3">
         <v>19340.2</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="3">
         <v>27391.25</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
+      <c r="A187" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="3">
         <v>19074.2</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="3">
         <v>26960.45</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
+      <c r="A188" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="3">
         <v>18250.099999999999</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="3">
         <v>25819.57</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
+      <c r="A189" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189" s="3">
         <v>18035.3</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="3">
         <v>26071.43</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
+      <c r="A190" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B190" s="2">
+      <c r="B190" s="3">
         <v>18151.8</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="3">
         <v>26515</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
+      <c r="A191" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191" s="3">
         <v>18691.8</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="3">
         <v>26907.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
+      <c r="A192" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B192" s="2">
+      <c r="B192" s="3">
         <v>17543.8</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D192" s="2">
+      <c r="D192" s="3">
         <v>25976.47</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="2" t="s">
+      <c r="A193" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193" s="3">
         <v>17240.099999999999</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="3">
         <v>25515.91</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
+      <c r="A194" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B194" s="3">
         <v>17696.599999999999</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194" s="3">
         <v>26238.5</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
+      <c r="A195" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195" s="3">
         <v>19324.8</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195" s="3">
         <v>17.93213961</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="3">
         <v>28332.14</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="2" t="s">
+      <c r="A196" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B196" s="3">
         <v>20115</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196" s="3">
         <v>29000</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
+      <c r="A197" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="3">
         <v>20043</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="3">
         <v>29583</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
+      <c r="A198" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198" s="3">
         <v>20328.900000000001</v>
       </c>
-      <c r="C198" s="2">
+      <c r="C198" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="3">
         <v>29578.18</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" s="2" t="s">
+      <c r="A199" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199" s="3">
         <v>20576.400000000001</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="3">
         <v>29564.55</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
+      <c r="A200" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200" s="3">
         <v>21584.6</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C200" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200" s="3">
         <v>31041.43</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
+      <c r="A201" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="3">
         <v>21642.7</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D201" s="2">
+      <c r="D201" s="3">
         <v>31226</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
+      <c r="A202" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202" s="3">
         <v>21406.3</v>
       </c>
-      <c r="C202" s="2">
+      <c r="C202" s="3">
         <v>17.93274005</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202" s="3">
         <v>31184.21</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A203" s="2" t="s">
+      <c r="A203" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203" s="3">
         <v>20460.8</v>
       </c>
-      <c r="C203" s="2">
+      <c r="C203" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203" s="3">
         <v>30295</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" s="2" t="s">
+      <c r="A204" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="3">
         <v>19982.900000000001</v>
       </c>
-      <c r="C204" s="2">
+      <c r="C204" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="3">
         <v>30382.19</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" s="2" t="s">
+      <c r="A205" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B205" s="2">
+      <c r="B205" s="3">
         <v>18584.099999999999</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205" s="3">
         <v>17.932740450000001</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="3">
         <v>28169.05</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" s="2" t="s">
+      <c r="A206" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B206" s="2">
+      <c r="B206" s="3">
         <v>19248.400000000001</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206" s="3">
         <v>17.93274048</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206" s="3">
         <v>29109.52</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
+      <c r="A207" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B207" s="2">
+      <c r="B207" s="3">
         <v>19914</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207" s="3">
         <v>17.93274048</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207" s="3">
         <v>29669.439999999999</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
+      <c r="A208" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B208" s="2">
+      <c r="B208" s="3">
         <v>19869</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C208" s="3">
         <v>17.93274048</v>
       </c>
-      <c r="D208" s="2">
+      <c r="D208" s="3">
         <v>29177.27</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="2" t="s">
+      <c r="A209" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B209" s="2">
+      <c r="B209" s="3">
         <v>20438.900000000001</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209" s="3">
         <v>17.932745600000001</v>
       </c>
-      <c r="D209" s="2">
+      <c r="D209" s="3">
         <v>29386.67</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
+      <c r="A210" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="3">
         <v>20095.7</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210" s="3">
         <v>17.932745600000001</v>
       </c>
-      <c r="D210" s="2">
+      <c r="D210" s="3">
         <v>28825</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
+      <c r="A211" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B211" s="2">
+      <c r="B211" s="3">
         <v>20348.5</v>
       </c>
-      <c r="C211" s="2">
+      <c r="C211" s="3">
         <v>17.932745600000001</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211" s="3">
         <v>29126.19</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" s="2" t="s">
+      <c r="A212" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B212" s="2">
+      <c r="B212" s="3">
         <v>19943.599999999999</v>
       </c>
-      <c r="C212" s="2">
+      <c r="C212" s="3">
         <v>17.93356095</v>
       </c>
-      <c r="D212" s="2">
+      <c r="D212" s="3">
         <v>29026.19</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" s="2" t="s">
+      <c r="A213" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213" s="3">
         <v>20691.900000000001</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C213" s="3">
         <v>17.93356095</v>
       </c>
-      <c r="D213" s="2">
+      <c r="D213" s="3">
         <v>29805</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
+      <c r="A214" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B214" s="2">
+      <c r="B214" s="3">
         <v>21240.5</v>
       </c>
-      <c r="C214" s="2">
+      <c r="C214" s="3">
         <v>17.93356095</v>
       </c>
-      <c r="D214" s="2">
+      <c r="D214" s="3">
         <v>30907.5</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
+      <c r="A215" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B215" s="2">
+      <c r="B215" s="3">
         <v>20666.900000000001</v>
       </c>
-      <c r="C215" s="2">
+      <c r="C215" s="3">
         <v>17.933420049999999</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215" s="3">
         <v>30768.42</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
+      <c r="A216" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B216" s="2">
+      <c r="B216" s="3">
         <v>20703.400000000001</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216" s="3">
         <v>17.933420049999999</v>
       </c>
-      <c r="D216" s="2">
+      <c r="D216" s="3">
         <v>30465.91</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
+      <c r="A217" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B217" s="2">
+      <c r="B217" s="3">
         <v>20421.599999999999</v>
       </c>
-      <c r="C217" s="2">
+      <c r="C217" s="3">
         <v>17.943420060000001</v>
       </c>
-      <c r="D217" s="2">
+      <c r="D217" s="3">
         <v>29726.25</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
+      <c r="A218" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B218" s="2">
+      <c r="B218" s="3">
         <v>21514.400000000001</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218" s="3">
         <v>17.943420060000001</v>
       </c>
-      <c r="D218" s="2">
+      <c r="D218" s="3">
         <v>30564.29</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A219" s="2" t="s">
+      <c r="A219" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219" s="3">
         <v>21522.5</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219" s="3">
         <v>17.94462111</v>
       </c>
-      <c r="D219" s="2">
+      <c r="D219" s="3">
         <v>30978.95</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A220" s="2" t="s">
+      <c r="A220" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B220" s="2">
+      <c r="B220" s="3">
         <v>21484.2</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220" s="3">
         <v>18.014645560000002</v>
       </c>
-      <c r="D220" s="2">
+      <c r="D220" s="3">
         <v>31036.84</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
+      <c r="A221" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B221" s="2">
+      <c r="B221" s="3">
         <v>21661.5</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221" s="3">
         <v>18.03464567</v>
       </c>
-      <c r="D221" s="2">
+      <c r="D221" s="3">
         <v>31752.38</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
+      <c r="A222" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B222" s="2">
+      <c r="B222" s="3">
         <v>21189.7</v>
       </c>
-      <c r="C222" s="2">
+      <c r="C222" s="3">
         <v>18.064694620000001</v>
       </c>
-      <c r="D222" s="2">
+      <c r="D222" s="3">
         <v>31827.27</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
+      <c r="A223" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B223" s="2">
+      <c r="B223" s="3">
         <v>21002.1</v>
       </c>
-      <c r="C223" s="2">
+      <c r="C223" s="3">
         <v>18.20469469</v>
       </c>
-      <c r="D223" s="2">
+      <c r="D223" s="3">
         <v>31355.71</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
+      <c r="A224" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B224" s="2">
+      <c r="B224" s="3">
         <v>20533.599999999999</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224" s="3">
         <v>18.424694850000002</v>
       </c>
-      <c r="D224" s="2">
+      <c r="D224" s="3">
         <v>30868.18</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
+      <c r="A225" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225" s="3">
         <v>20162.3</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225" s="3">
         <v>18.644694990000001</v>
       </c>
-      <c r="D225" s="2">
+      <c r="D225" s="3">
         <v>30454.76</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
+      <c r="A226" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B226" s="2">
+      <c r="B226" s="3">
         <v>20343.400000000001</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226" s="3">
         <v>18.854695150000001</v>
       </c>
-      <c r="D226" s="2">
+      <c r="D226" s="3">
         <v>31198.89</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
+      <c r="A227" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B227" s="2">
+      <c r="B227" s="3">
         <v>20815.5</v>
       </c>
-      <c r="C227" s="2">
+      <c r="C227" s="3">
         <v>19.034695599999999</v>
       </c>
-      <c r="D227" s="2">
+      <c r="D227" s="3">
         <v>31842.5</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
+      <c r="A228" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B228" s="2">
+      <c r="B228" s="3">
         <v>21150</v>
       </c>
-      <c r="C228" s="2">
+      <c r="C228" s="3">
         <v>19.244780160000001</v>
       </c>
-      <c r="D228" s="2">
+      <c r="D228" s="3">
         <v>31750</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
+      <c r="A229" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B229" s="2">
+      <c r="B229" s="3">
         <v>21689.9</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229" s="3">
         <v>19.30478059</v>
       </c>
-      <c r="D229" s="2">
+      <c r="D229" s="3">
         <v>31813.75</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
+      <c r="A230" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B230" s="2">
+      <c r="B230" s="3">
         <v>22686.2</v>
       </c>
-      <c r="C230" s="2">
+      <c r="C230" s="3">
         <v>19.5147808</v>
       </c>
-      <c r="D230" s="2">
+      <c r="D230" s="3">
         <v>32760.43</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
+      <c r="A231" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B231" s="2">
+      <c r="B231" s="3">
         <v>23253.1</v>
       </c>
-      <c r="C231" s="2">
+      <c r="C231" s="3">
         <v>19.574656470000001</v>
       </c>
-      <c r="D231" s="2">
+      <c r="D231" s="3">
         <v>33647.5</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
+      <c r="A232" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B232" s="2">
+      <c r="B232" s="3">
         <v>23070.91</v>
       </c>
-      <c r="C232" s="2">
+      <c r="C232" s="3">
         <v>19.694656569999999</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232" s="3">
         <v>32828.949999999997</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="2" t="s">
+      <c r="A233" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B233" s="2">
+      <c r="B233" s="3">
         <v>23021.599999999999</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233" s="3">
         <v>19.874593870000002</v>
       </c>
-      <c r="D233" s="2">
+      <c r="D233" s="3">
         <v>32571.05</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
+      <c r="A234" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B234" s="2">
+      <c r="B234" s="3">
         <v>22958.7</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234" s="3">
         <v>19.874593870000002</v>
       </c>
-      <c r="D234" s="2">
+      <c r="D234" s="3">
         <v>32593.18</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
+      <c r="A235" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B235" s="2">
+      <c r="B235" s="3">
         <v>24304.5</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235" s="3">
         <v>19.874593879999999</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235" s="3">
         <v>33339.47</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
+      <c r="A236" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B236" s="2">
+      <c r="B236" s="3">
         <v>25505.25</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236" s="3">
         <v>19.874593879999999</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236" s="3">
         <v>34293.480000000003</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
+      <c r="A237" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B237" s="2">
+      <c r="B237" s="3">
         <v>27338.68</v>
       </c>
-      <c r="C237" s="2">
+      <c r="C237" s="3">
         <v>19.874593879999999</v>
       </c>
-      <c r="D237" s="2">
+      <c r="D237" s="3">
         <v>36745.24</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
+      <c r="A238" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B238" s="2">
+      <c r="B238" s="3">
         <v>26650.02</v>
       </c>
-      <c r="C238" s="2">
+      <c r="C238" s="3">
         <v>19.874593879999999</v>
       </c>
-      <c r="D238" s="2">
+      <c r="D238" s="3">
         <v>37484.21</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
+      <c r="A239" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B239" s="2">
+      <c r="B239" s="3">
         <v>27011.767</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239" s="3">
         <v>20.114668160000001</v>
       </c>
-      <c r="D239" s="2">
+      <c r="D239" s="3">
         <v>38005.56</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="2" t="s">
+      <c r="A240" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B240" s="2">
+      <c r="B240" s="3">
         <v>26748.76</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C240" s="3">
         <v>20.354653160000002</v>
       </c>
-      <c r="D240" s="2">
+      <c r="D240" s="3">
         <v>38718.5</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="2" t="s">
+      <c r="A241" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B241" s="2">
+      <c r="B241" s="3">
         <v>27830.78</v>
       </c>
-      <c r="C241" s="2">
+      <c r="C241" s="3">
         <v>20.414653730000001</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241" s="3">
         <v>38695.24</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
+      <c r="A242" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B242" s="2">
+      <c r="B242" s="3">
         <v>28997.49</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242" s="3">
         <v>20.414669119999999</v>
       </c>
-      <c r="D242" s="2">
+      <c r="D242" s="3">
         <v>39987.74</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="2" t="s">
+      <c r="A243" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B243" s="2">
+      <c r="B243" s="3">
         <v>29896.83</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243" s="3">
         <v>20.634670710000002</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="3">
         <v>41174.35</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="2" t="s">
+      <c r="A244" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B244" s="2">
+      <c r="B244" s="3">
         <v>30578.16</v>
       </c>
-      <c r="C244" s="2">
+      <c r="C244" s="3">
         <v>20.99472669</v>
       </c>
-      <c r="D244" s="2">
+      <c r="D244" s="3">
         <v>42179.57</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="2" t="s">
+      <c r="A245" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B245" s="2">
+      <c r="B245" s="3">
         <v>32277.3</v>
       </c>
-      <c r="C245" s="2">
+      <c r="C245" s="3">
         <v>21.054800440000001</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245" s="3">
         <v>48723.22</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="2" t="s">
+      <c r="A246" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B246" s="2">
+      <c r="B246" s="3">
         <v>32897.699999999997</v>
       </c>
-      <c r="C246" s="2">
+      <c r="C246" s="3">
         <v>21.14480524</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="3">
         <v>48723.22</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="2" t="s">
+      <c r="A247" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B247" s="2">
+      <c r="B247" s="3">
         <v>33905.43</v>
       </c>
-      <c r="C247" s="2">
+      <c r="C247" s="3">
         <v>21.264805490000001</v>
       </c>
-      <c r="D247" s="2">
+      <c r="D247" s="3">
         <v>47300.19</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" s="2" t="s">
+      <c r="A248" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B248" s="2">
+      <c r="B248" s="3">
         <v>37624.69</v>
       </c>
-      <c r="C248" s="2">
+      <c r="C248" s="3">
         <v>21.354789889999999</v>
       </c>
-      <c r="D248" s="2">
+      <c r="D248" s="3">
         <v>49937.35</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" s="2" t="s">
+      <c r="A249" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B249" s="2">
+      <c r="B249" s="3">
         <v>37847.93</v>
       </c>
-      <c r="C249" s="2">
+      <c r="C249" s="3">
         <v>21.48479012</v>
       </c>
-      <c r="D249" s="2">
+      <c r="D249" s="3">
         <v>53144.75</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="2" t="s">
+      <c r="A250" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B250" s="2">
+      <c r="B250" s="3">
         <v>36428.65</v>
       </c>
-      <c r="C250" s="2">
+      <c r="C250" s="3">
         <v>21.48479012</v>
       </c>
-      <c r="D250" s="2">
+      <c r="D250" s="3">
         <v>50904.5</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
+      <c r="A251" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B251" s="2">
+      <c r="B251" s="3">
         <v>36489.660000000003</v>
       </c>
-      <c r="C251" s="2">
+      <c r="C251" s="3">
         <v>21.544790129999999</v>
       </c>
-      <c r="D251" s="2">
+      <c r="D251" s="3">
         <v>50659.43</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252" s="2" t="s">
+      <c r="A252" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B252" s="2">
+      <c r="B252" s="3">
         <v>35192.449999999997</v>
       </c>
-      <c r="C252" s="2">
+      <c r="C252" s="3">
         <v>21.634790169999999</v>
       </c>
-      <c r="D252" s="2">
+      <c r="D252" s="3">
         <v>50453.32</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253" s="2" t="s">
+      <c r="A253" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B253" s="2">
+      <c r="B253" s="3">
         <v>36957.919999999998</v>
       </c>
-      <c r="C253" s="2">
+      <c r="C253" s="3">
         <v>21.754794489999998</v>
       </c>
-      <c r="D253" s="2">
+      <c r="D253" s="3">
         <v>49479.14</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A254" s="2" t="s">
+      <c r="A254" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B254" s="2">
+      <c r="B254" s="3">
         <v>36491.93</v>
       </c>
-      <c r="C254" s="2">
+      <c r="C254" s="3">
         <v>21.754794489999998</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254" s="3">
         <v>49620.9</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255" s="2" t="s">
+      <c r="A255" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B255" s="2">
+      <c r="B255" s="3">
         <v>35421.019999999997</v>
       </c>
-      <c r="C255" s="2">
+      <c r="C255" s="3">
         <v>22.11484591</v>
       </c>
-      <c r="D255" s="2">
+      <c r="D255" s="3">
         <v>47166.85</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256" s="2" t="s">
+      <c r="A256" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B256" s="2">
+      <c r="B256" s="3">
         <v>33880.129999999997</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256" s="3">
         <v>22.35492958</v>
       </c>
-      <c r="D256" s="2">
+      <c r="D256" s="3">
         <v>44741.33</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257" s="2" t="s">
+      <c r="A257" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B257" s="2">
+      <c r="B257" s="3">
         <v>35463.519999999997</v>
       </c>
-      <c r="C257" s="2">
+      <c r="C257" s="3">
         <v>22.35492958</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257" s="3">
         <v>46486.16</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258" s="2" t="s">
+      <c r="A258" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B258" s="2">
+      <c r="B258" s="3">
         <v>38277.22</v>
       </c>
-      <c r="C258" s="2">
+      <c r="C258" s="3">
         <v>22.384929580000001</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="3">
         <v>47931.95</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A259" s="2" t="s">
+      <c r="A259" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B259" s="2">
+      <c r="B259" s="3">
         <v>35745.24</v>
       </c>
-      <c r="C259" s="2">
+      <c r="C259" s="3">
         <v>22.62493173</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="3">
         <v>47937.64</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A260" s="2" t="s">
+      <c r="A260" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B260" s="2">
+      <c r="B260" s="3">
         <v>37571.089999999997</v>
       </c>
-      <c r="C260" s="2">
+      <c r="C260" s="3">
         <v>22.8649381</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="3">
         <v>47739.95</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
+      <c r="A261" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B261" s="2">
+      <c r="B261" s="3">
         <v>37738.76</v>
       </c>
-      <c r="C261" s="2">
+      <c r="C261" s="3">
         <v>23.314957249999999</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="3">
         <v>47165.7</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="2" t="s">
+      <c r="A262" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B262" s="2">
+      <c r="B262" s="3">
         <v>37389.480000000003</v>
       </c>
-      <c r="C262" s="2">
+      <c r="C262" s="3">
         <v>23.914959469999999</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="3">
         <v>46594.95</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="2" t="s">
+      <c r="A263" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B263" s="2">
+      <c r="B263" s="3">
         <v>38269.300000000003</v>
       </c>
-      <c r="C263" s="2">
+      <c r="C263" s="3">
         <v>24.03495947</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="3">
         <v>47206.9</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="2" t="s">
+      <c r="A264" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B264" s="2">
+      <c r="B264" s="3">
         <v>38777.370000000003</v>
       </c>
-      <c r="C264" s="2">
+      <c r="C264" s="3">
         <v>24.124959489999998</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="3">
         <v>48177.45</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="2" t="s">
+      <c r="A265" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B265" s="2">
+      <c r="B265" s="3">
         <v>39404.519999999997</v>
       </c>
-      <c r="C265" s="2">
+      <c r="C265" s="3">
         <v>24.244984299999999</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="3">
         <v>47945.91</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="2" t="s">
+      <c r="A266" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B266" s="2">
+      <c r="B266" s="3">
         <v>39086.53</v>
       </c>
-      <c r="C266" s="2">
+      <c r="C266" s="3">
         <v>24.28738117</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="3">
         <v>48015.839999999997</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="2" t="s">
+      <c r="A267" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B267" s="2">
+      <c r="B267" s="3">
         <v>41337.58</v>
       </c>
-      <c r="C267" s="2">
+      <c r="C267" s="3">
         <v>24.36897574</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="3">
         <v>49308.7</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="2" t="s">
+      <c r="A268" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B268" s="2">
+      <c r="B268" s="3">
         <v>42551.13</v>
       </c>
-      <c r="C268" s="2">
+      <c r="C268" s="3">
         <v>24.448141190000001</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="3">
         <v>51782.33</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269" s="2" t="s">
+      <c r="A269" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B269" s="2">
+      <c r="B269" s="3">
         <v>42106.64</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C269" s="3">
         <v>24.478182400000001</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="3">
         <v>51991.63</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270" s="2" t="s">
+      <c r="A270" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B270" s="2">
+      <c r="B270" s="3">
         <v>41065.58</v>
       </c>
-      <c r="C270" s="2">
+      <c r="C270" s="3">
         <v>24.598198060000001</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="3">
         <v>50888.24</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271" s="2" t="s">
+      <c r="A271" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B271" s="2">
+      <c r="B271" s="3">
         <v>40389.599999999999</v>
       </c>
-      <c r="C271" s="2">
+      <c r="C271" s="3">
         <v>24.6883947</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="3">
         <v>46519.23</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272" s="2" t="s">
+      <c r="A272" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B272" s="2">
+      <c r="B272" s="3">
         <v>39639.57</v>
       </c>
-      <c r="C272" s="2">
+      <c r="C272" s="3">
         <v>25.11917876</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="3">
         <v>44034.38</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273" s="2" t="s">
+      <c r="A273" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B273" s="2">
+      <c r="B273" s="3">
         <v>39590.97</v>
       </c>
-      <c r="C273" s="2">
+      <c r="C273" s="3">
         <v>25.11917876</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="3">
         <v>44731.5</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274" s="2" t="s">
+      <c r="A274" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B274" s="2">
+      <c r="B274" s="3">
         <v>37604.910000000003</v>
       </c>
-      <c r="C274" s="2">
+      <c r="C274" s="3">
         <v>25.24971468</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="3">
         <v>43279.91</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="2" t="s">
+      <c r="A275" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B275" s="2">
+      <c r="B275" s="3">
         <v>37496.01</v>
       </c>
-      <c r="C275" s="2">
+      <c r="C275" s="3">
         <v>25.27971535</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="3">
         <v>43923.19</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="2" t="s">
+      <c r="A276" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B276" s="2">
+      <c r="B276" s="3">
         <v>39876.980000000003</v>
       </c>
-      <c r="C276" s="2">
+      <c r="C276" s="3">
         <v>25.27971535</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="3">
         <v>44967.33</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="2" t="s">
+      <c r="A277" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B277" s="2">
+      <c r="B277" s="3">
         <v>41290.89</v>
       </c>
-      <c r="C277" s="2">
+      <c r="C277" s="3">
         <v>25.314519799999999</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="3">
         <v>46776.67</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="2" t="s">
+      <c r="A278" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B278" s="2">
+      <c r="B278" s="3">
         <v>43836.9</v>
       </c>
-      <c r="C278" s="2">
+      <c r="C278" s="3">
         <v>25.314519799999999</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="3">
         <v>48803.24</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="2" t="s">
+      <c r="A279" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B279" s="2">
+      <c r="B279" s="3">
         <v>41630.949999999997</v>
       </c>
-      <c r="C279" s="2">
+      <c r="C279" s="3">
         <v>25.434587870000001</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="3">
         <v>49056.35</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="2" t="s">
+      <c r="A280" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B280" s="2">
+      <c r="B280" s="3">
         <v>45200.31</v>
       </c>
-      <c r="C280" s="2">
+      <c r="C280" s="3">
         <v>25.548157719999999</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="3">
         <v>50009.57</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="2" t="s">
+      <c r="A281" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B281" s="2">
+      <c r="B281" s="3">
         <v>45585.45</v>
       </c>
-      <c r="C281" s="2">
+      <c r="C281" s="3">
         <v>25.548157719999999</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="3">
         <v>52160.59</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282" s="2" t="s">
+      <c r="A282" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B282" s="2">
+      <c r="B282" s="3">
         <v>44999.05</v>
       </c>
-      <c r="C282" s="2">
+      <c r="C282" s="3">
         <v>25.608311929999999</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="3">
         <v>52532.91</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283" s="2" t="s">
+      <c r="A283" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B283" s="3">
         <v>43832.28</v>
       </c>
-      <c r="C283" s="2">
+      <c r="C283" s="3">
         <v>25.638311959999999</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="3">
         <v>51216.95</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284" s="2" t="s">
+      <c r="A284" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B284" s="3">
         <v>45109.48</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C284" s="3">
         <v>25.647509880000001</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="3">
         <v>51180.33</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285" s="2" t="s">
+      <c r="A285" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B285" s="3">
         <v>45060</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C285" s="3">
         <v>25.7075107</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285" s="3">
         <v>50917.05</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286" s="2" t="s">
+      <c r="A286" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B286" s="3">
         <v>43341.94</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C286" s="3">
         <v>25.74590031</v>
       </c>
-      <c r="D286" s="2">
+      <c r="D286" s="3">
         <v>50965.75</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287" s="2" t="s">
+      <c r="A287" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B287" s="3">
         <v>46448.82</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C287" s="3">
         <v>25.835900429999999</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="3">
         <v>55317.1</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288" s="2" t="s">
+      <c r="A288" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B288" s="3">
         <v>47596.32</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C288" s="3">
         <v>25.835900429999999</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="3">
         <v>60827.55</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289" s="2" t="s">
+      <c r="A289" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="3">
         <v>47955.56</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C289" s="3">
         <v>25.835900429999999</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="3">
         <v>62277.1</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290" s="2" t="s">
+      <c r="A290" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B290" s="3">
         <v>47967.45</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290" s="3">
         <v>26.087060640000001</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="3">
         <v>62313.32</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291" s="2" t="s">
+      <c r="A291" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="3">
         <v>48047.839999999997</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C291" s="3">
         <v>26.267060910000001</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="3">
         <v>62057.24</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292" s="2" t="s">
+      <c r="A292" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B292" s="3">
         <v>52674.83</v>
       </c>
-      <c r="C292" s="2">
+      <c r="C292" s="3">
         <v>26.431049059999999</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292" s="3">
         <v>65176.21</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
+      <c r="A293" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="3">
         <v>55888.39</v>
       </c>
-      <c r="C293" s="2">
+      <c r="C293" s="3">
         <v>26.611049059999999</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293" s="3">
         <v>71492.5</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294" s="2" t="s">
+      <c r="A294" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B294" s="2">
+      <c r="B294" s="3">
         <v>56501.29</v>
       </c>
-      <c r="C294" s="2">
+      <c r="C294" s="3">
         <v>26.731049689999999</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294" s="3">
         <v>72188.38</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295" s="2" t="s">
+      <c r="A295" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B295" s="2">
+      <c r="B295" s="3">
         <v>56528.43</v>
       </c>
-      <c r="C295" s="2">
+      <c r="C295" s="3">
         <v>27.03105687</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295" s="3">
         <v>71595.16</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296" s="2" t="s">
+      <c r="A296" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296" s="3">
         <v>58524.54</v>
       </c>
-      <c r="C296" s="2">
+      <c r="C296" s="3">
         <v>27.205214089999998</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296" s="3">
         <v>71556.7</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297" s="2" t="s">
+      <c r="A297" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297" s="3">
         <v>61742.21</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C297" s="3">
         <v>27.295226299999999</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="3">
         <v>70400.429999999993</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298" s="2" t="s">
+      <c r="A298" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298" s="3">
         <v>65749.490000000005</v>
       </c>
-      <c r="C298" s="2">
+      <c r="C298" s="3">
         <v>27.445193530000001</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298" s="3">
         <v>72851.520000000004</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299" s="2" t="s">
+      <c r="A299" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B299" s="2">
+      <c r="B299" s="3">
         <v>69750.570000000007</v>
       </c>
-      <c r="C299" s="2">
+      <c r="C299" s="3">
         <v>27.900005889999999</v>
       </c>
-      <c r="D299" s="2">
+      <c r="D299" s="3">
         <v>76680.679999999993</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300" s="2" t="s">
+      <c r="A300" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B300" s="2">
+      <c r="B300" s="3">
         <v>67212.009999999995</v>
       </c>
-      <c r="C300" s="2">
+      <c r="C300" s="3">
         <v>28.169974750000002</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="3">
         <v>76263.11</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A301" s="2" t="s">
+      <c r="A301" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B301" s="2">
+      <c r="B301" s="3">
         <v>66148.45</v>
       </c>
-      <c r="C301" s="2">
+      <c r="C301" s="3">
         <v>28.169974750000002</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="3">
         <v>76263.81</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A302" s="2" t="s">
+      <c r="A302" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B302" s="2">
+      <c r="B302" s="3">
         <v>70892.84</v>
       </c>
-      <c r="C302" s="2">
+      <c r="C302" s="3">
         <v>28.260766950000001</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302" s="3">
         <v>78642.13</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A303" s="2" t="s">
+      <c r="A303" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B303" s="2">
+      <c r="B303" s="3">
         <v>73272.259999999995</v>
       </c>
-      <c r="C303" s="2">
+      <c r="C303" s="3">
         <v>28.260766950000001</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303" s="3">
         <v>84888.4</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A304" s="2" t="s">
+      <c r="A304" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B304" s="2">
+      <c r="B304" s="3">
         <v>78176.350000000006</v>
       </c>
-      <c r="C304" s="2">
+      <c r="C304" s="3">
         <v>28.279272779999999</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304" s="3">
         <v>86902.26</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
+      <c r="A305" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B305" s="2">
+      <c r="B305" s="3">
         <v>84117.97</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C305" s="3">
         <v>28.279272779999999</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305" s="3">
         <v>93147.63</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306" s="2" t="s">
+      <c r="A306" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B306" s="2">
+      <c r="B306" s="3">
         <v>83418.11</v>
       </c>
-      <c r="C306" s="2">
+      <c r="C306" s="3">
         <v>28.27929198</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306" s="3">
         <v>94673.95</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307" s="2" t="s">
+      <c r="A307" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B307" s="2">
+      <c r="B307" s="3">
         <v>83308.179999999993</v>
       </c>
-      <c r="C307" s="2">
+      <c r="C307" s="3">
         <v>28.29208856</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="3">
         <v>97091.43</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308" s="2" t="s">
+      <c r="A308" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B308" s="2">
+      <c r="B308" s="3">
         <v>84136.99</v>
       </c>
-      <c r="C308" s="2">
+      <c r="C308" s="3">
         <v>28.29208856</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="3">
         <v>97587.43</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309" s="2" t="s">
+      <c r="A309" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B309" s="2">
+      <c r="B309" s="3">
         <v>87316.03</v>
       </c>
-      <c r="C309" s="2">
+      <c r="C309" s="3">
         <v>28.29208856</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309" s="3">
         <v>99683.47</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310" s="2" t="s">
+      <c r="A310" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B310" s="2">
+      <c r="B310" s="3">
         <v>97464.66</v>
       </c>
-      <c r="C310" s="2">
+      <c r="C310" s="3">
         <v>28.2984869</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310" s="3">
         <v>109531.32</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311" s="2" t="s">
+      <c r="A311" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B311" s="2">
+      <c r="B311" s="3">
         <v>101725.56</v>
       </c>
-      <c r="C311" s="2">
+      <c r="C311" s="3">
         <v>28.2984869</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311" s="3">
         <v>122294.3</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312" s="2" t="s">
+      <c r="A312" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B312" s="2">
+      <c r="B312" s="3">
         <v>106740</v>
       </c>
-      <c r="C312" s="2">
+      <c r="C312" s="3">
         <v>28.2984869</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312" s="3">
         <v>122834</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313" s="2" t="s">
+      <c r="A313" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B313" s="2">
+      <c r="B313" s="3">
         <v>111262</v>
       </c>
-      <c r="C313" s="2">
+      <c r="C313" s="3">
         <v>28.30368764</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313" s="3">
         <v>131322.54999999999</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314" s="2" t="s">
+      <c r="A314" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B314" s="2">
+      <c r="B314" s="3">
         <v>126904</v>
       </c>
-      <c r="C314" s="2">
+      <c r="C314" s="3">
         <v>28.303707169999999</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314" s="3">
         <v>146169.79999999999</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315" s="2" t="s">
+      <c r="A315" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B315" s="2">
+      <c r="B315" s="3">
         <v>131630</v>
       </c>
-      <c r="C315" s="2">
+      <c r="C315" s="3">
         <v>28.30370924</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="3">
         <v>154370.4</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316" s="2" t="s">
+      <c r="A316" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B316" s="2">
+      <c r="B316" s="3">
         <v>115395</v>
       </c>
-      <c r="C316" s="2">
+      <c r="C316" s="3">
         <v>28.309307700000002</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316" s="3">
         <v>147395</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>